--- a/extenbooks/ES2304_extenbook.xlsx
+++ b/extenbooks/ES2304_extenbook.xlsx
@@ -726,7 +726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A150"/>
+  <dimension ref="A1:A185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -786,7 +786,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: study_complete</t>
         </is>
       </c>
     </row>
@@ -1608,6 +1608,239 @@
       <c r="A150" t="inlineStr">
         <is>
           <t>explicitly excluded per Anu Framework no-fabrication rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>## 6. Conceptual continuity vs adjacent concepts</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>The data object `RMB misalignment estimates compiled from 4 literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>reviews, filtered to extended-PPP methodology` measures `equilibrium</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>real-exchange-rate deviation under BEER-style reduced-form regressions`</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>rather than `IMF EBA model output` or `simple PPP-deviation` because:</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>- Source agency choice: paper note 17 explicitly names Cline &amp; Williamson</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2007 (PIIE), Dunaway-Li 2005 (IMF WP), Cheung-Chinn-Fujii 2010a (La</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Follette WP), Cheung 2012 (CESifo WP). No other reviews are</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  substituted — even if they would expand coverage, the paper's</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  compilation rule restricts to these four.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>- Methodology continuity: each cited estimate already used the BEER-style</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  extended-PPP methodology when published 1999-2010. The compilation</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  preserves both the originating-estimate methodology label and the</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  paper's filter to extended-PPP studies only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>- Disambiguation: extended-PPP (ES2304) ≠ macroeconomic-balance (ES2305)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  even when sampled from the same 4 reviews; extended-PPP regression on</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  fundamentals ≠ raw PPP deviation; the IMF EBA model (post-2014) is</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  methodologically a *different empirical object*, not a continuation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>The book's original concept (Weber &amp; Shaikh 2020 note 17, p. 448, verbatim)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>was: "Figure 4 and Figure 5 are compiled based on the selection of</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>studies contained in the four literature reviews ... If a source reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>more than one estimate of the RMB misalignment, each estimate was treated</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>as a separate data point in the scatter plots." The modern series</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>preserves the 4-review compilation rule and the methodology filter while</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>permitting the v1.0 truncation to two paper-text-named endpoints (+50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Coudert-Couharde 2007; -36% Cheung 2012). This is NOT a proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>substitution forbidden by the No-Proxy rule because the underlying</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>estimates are verbatim from their cited working papers; v1.1 literature</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>extraction will populate the remaining ~30-35 scatter points from the</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>same 4 sources. The series is intrinsically non-extensible past 2012</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>because the paper's compilation universe is fixed (`extension_status:</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>not_applicable_literature_compilation`).</t>
         </is>
       </c>
     </row>
@@ -1907,11 +2140,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1934,54 +2167,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[5, 6, 7]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>{"dpr": "Technical/docs/series/ES2304_DPR.md", "epr": "Technical/docs/series/ES2304_EPR.md", "loader": "Technical/code/L01_loaders/L01_ES2304_load.py", "processor": "Technical/code/P02_processors/P02_ES2304_construct.py", "validator": "Technical/code/V03_validators/V03_ES2304_validate.py"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>last_updated</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>opus-fanout-ES</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
